--- a/data/KTLEV (TRY).xlsx
+++ b/data/KTLEV (TRY).xlsx
@@ -12,6 +12,28 @@
     <sheet name="Nakit Akış (Yıllıklan.)" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -381,9 +403,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:N39"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -395,6 +417,8 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -402,36 +426,42 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -445,36 +475,42 @@
         <v xml:space="preserve">    Nakit, Nakit Benzerleri ve Merkez Bankası</v>
       </c>
       <c r="B3">
+        <v>5011991665</v>
+      </c>
+      <c r="C3">
+        <v>8517955658</v>
+      </c>
+      <c r="D3">
         <v>5882196682</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>3556608602</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>2765931522</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>2321418795</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>2214370738</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>1178623668</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>816792332</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>801731439</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>338328609</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>312490812</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>180527418</v>
       </c>
     </row>
@@ -483,36 +519,42 @@
         <v xml:space="preserve">    İtfa Edilmiş Maliyet ile Ölçülen Finansal Varlıklar (Net)</v>
       </c>
       <c r="B4">
+        <v>27418457713</v>
+      </c>
+      <c r="C4">
+        <v>18969743056</v>
+      </c>
+      <c r="D4">
         <v>10919128088</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>7625123040</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>5696678844</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>5820765277</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>4154974890</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>2014588898</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>1580586960</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>980689954</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>783485567</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>655772285</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>462968593</v>
       </c>
     </row>
@@ -521,36 +563,42 @@
         <v xml:space="preserve">    Tasarruf Finansman Alacakları</v>
       </c>
       <c r="B5">
+        <v>27310691126</v>
+      </c>
+      <c r="C5">
+        <v>18903620456</v>
+      </c>
+      <c r="D5">
         <v>10868723373</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>7590781494</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>5681393563</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>5791287743</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>4126258154</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>2008557533</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>1567227928</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>975737377</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>779842941</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>653169958</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>460901200</v>
       </c>
     </row>
@@ -564,36 +612,42 @@
         <v xml:space="preserve">    Takipteki Alacaklar</v>
       </c>
       <c r="B7">
+        <v>131207141</v>
+      </c>
+      <c r="C7">
+        <v>71844452</v>
+      </c>
+      <c r="D7">
         <v>56993907</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>39472582</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>19416270</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>41588710</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>37216130</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>7386969</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>16596602</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>6181359</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>4560948</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>3370923</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>3751792</v>
       </c>
     </row>
@@ -602,36 +656,42 @@
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları / Özel Karşılıklar (-)</v>
       </c>
       <c r="B8">
+        <v>-23440554</v>
+      </c>
+      <c r="C8">
+        <v>-5721852</v>
+      </c>
+      <c r="D8">
         <v>-6589192</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>-5131036</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>-4130989</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>-12111176</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>-8499394</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>-1355604</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>-3237570</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>-1228782</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>-918322</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>-768596</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>-1684399</v>
       </c>
     </row>
@@ -642,25 +702,28 @@
       <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
       <c r="D9">
         <v>0</v>
       </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>230000000</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
     </row>
@@ -669,36 +732,42 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar (Net)</v>
       </c>
       <c r="B10">
+        <v>971956743</v>
+      </c>
+      <c r="C10">
+        <v>993810603</v>
+      </c>
+      <c r="D10">
         <v>605993628</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>613658232</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>484169021</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>659326224</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>444852189</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>316904863</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>319077457</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>316039370</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>183965871</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>174078699</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>169243411</v>
       </c>
     </row>
@@ -707,36 +776,42 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar (Net)</v>
       </c>
       <c r="B11">
+        <v>310064755</v>
+      </c>
+      <c r="C11">
+        <v>292135005</v>
+      </c>
+      <c r="D11">
         <v>269604070</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>250785502</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>239041309</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>656623112</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>650662935</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>44855412</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>42462486</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>39414163</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>38683533</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>36195189</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>8028410</v>
       </c>
     </row>
@@ -745,10 +820,10 @@
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller (Net)</v>
       </c>
       <c r="B12">
-        <v>4082500002</v>
+        <v>4406250000</v>
       </c>
       <c r="C12">
-        <v>4082500002</v>
+        <v>4320500000</v>
       </c>
       <c r="D12">
         <v>4082500002</v>
@@ -757,13 +832,13 @@
         <v>4082500002</v>
       </c>
       <c r="F12">
+        <v>4082500002</v>
+      </c>
+      <c r="G12">
         <v>4082500000</v>
       </c>
-      <c r="G12">
-        <v>50500000</v>
-      </c>
       <c r="H12">
-        <v>50500000</v>
+        <v>4082500000</v>
       </c>
       <c r="I12">
         <v>50500000</v>
@@ -775,6 +850,12 @@
         <v>50500000</v>
       </c>
       <c r="L12">
+        <v>50500000</v>
+      </c>
+      <c r="M12">
+        <v>50500000</v>
+      </c>
+      <c r="N12">
         <v>50500000</v>
       </c>
     </row>
@@ -785,28 +866,31 @@
       <c r="B13">
         <v>0</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>18461</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>18461</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
     </row>
@@ -815,30 +899,33 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
+        <v>670671</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>23115735</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>86545640</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
-      <c r="K14">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>0</v>
       </c>
     </row>
@@ -847,36 +934,42 @@
         <v xml:space="preserve">    Diğer Aktifler</v>
       </c>
       <c r="B15">
+        <v>2697818650</v>
+      </c>
+      <c r="C15">
+        <v>1449099976</v>
+      </c>
+      <c r="D15">
         <v>979846258</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>993613613</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>1728964740</v>
       </c>
-      <c r="E15">
-        <v>1727438631</v>
-      </c>
-      <c r="F15">
+      <c r="G15">
+        <v>1727438633</v>
+      </c>
+      <c r="H15">
         <v>1933257018</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>294422212</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>220142914</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>144297189</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>182069863</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>110070243</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>129976586</v>
       </c>
     </row>
@@ -885,36 +978,42 @@
         <v xml:space="preserve">    (ARA TOPLAM) 1</v>
       </c>
       <c r="B16">
+        <v>56679474844</v>
+      </c>
+      <c r="C16">
+        <v>47455977200</v>
+      </c>
+      <c r="D16">
         <v>34980348406</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>24252501533</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>18831977956</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>18914951780</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>15629654483</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>5654858818</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>4745768868</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>3435987305</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>2168246346</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>1764420701</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>1001244418</v>
       </c>
     </row>
@@ -925,25 +1024,28 @@
       <c r="B17">
         <v>0</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
       <c r="D17">
         <v>0</v>
       </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
       <c r="F17">
         <v>0</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
       <c r="H17">
         <v>0</v>
       </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
     </row>
@@ -952,36 +1054,42 @@
         <v xml:space="preserve">    TOPLAM VARLIKLAR</v>
       </c>
       <c r="B18">
+        <v>56679474844</v>
+      </c>
+      <c r="C18">
+        <v>47455977200</v>
+      </c>
+      <c r="D18">
         <v>34980348406</v>
       </c>
-      <c r="C18">
+      <c r="E18">
         <v>24252501533</v>
       </c>
-      <c r="D18">
+      <c r="F18">
         <v>18831977956</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>18914951780</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>15629654483</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>5654858818</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>4745768868</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>3435987305</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>2168246346</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>1764420701</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>1001244418</v>
       </c>
     </row>
@@ -990,36 +1098,42 @@
         <v xml:space="preserve">    YÜKÜMLÜLÜKLER TOPLAMI</v>
       </c>
       <c r="B19">
+        <v>40860172861</v>
+      </c>
+      <c r="C19">
+        <v>34999489997</v>
+      </c>
+      <c r="D19">
         <v>25935450639</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>17685953327</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>13781734492</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>14828567715</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>12245365598</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>4037994821</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>3157367721</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>2272240043</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>1384088856</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>977526113</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>720022048</v>
       </c>
     </row>
@@ -1030,28 +1144,31 @@
       <c r="B20">
         <v>0</v>
       </c>
-      <c r="C20">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>261274484</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <v>620696518</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>925125572</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>1197239575</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>0</v>
       </c>
     </row>
@@ -1062,25 +1179,28 @@
       <c r="B21">
         <v>0</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
       <c r="D21">
         <v>0</v>
       </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
       <c r="H21">
         <v>0</v>
       </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>0</v>
       </c>
     </row>
@@ -1089,36 +1209,42 @@
         <v xml:space="preserve">    Tasarruf Fon Havuzundan Borçlar</v>
       </c>
       <c r="B22">
+        <v>33547324638</v>
+      </c>
+      <c r="C22">
+        <v>28264360209</v>
+      </c>
+      <c r="D22">
         <v>21898546657</v>
       </c>
-      <c r="C22">
+      <c r="E22">
         <v>14677818151</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <v>10245138000</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>10480917928</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>7937844557</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>3399332475</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>2318036802</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>1745972671</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>1063756098</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>784071827</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>553689645</v>
       </c>
     </row>
@@ -1127,36 +1253,42 @@
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlar</v>
       </c>
       <c r="B23">
+        <v>574643186</v>
+      </c>
+      <c r="C23">
+        <v>608198327</v>
+      </c>
+      <c r="D23">
         <v>303089987</v>
       </c>
-      <c r="C23">
+      <c r="E23">
         <v>318684741</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>345093747</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>529109404</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>324175365</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>182904089</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>185352634</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>199468877</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>77621721</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>83737328</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>96465579</v>
       </c>
     </row>
@@ -1167,25 +1299,28 @@
       <c r="B24">
         <v>0</v>
       </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
       <c r="D24">
         <v>0</v>
       </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
       <c r="H24">
         <v>0</v>
       </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>0</v>
       </c>
     </row>
@@ -1194,36 +1329,42 @@
         <v xml:space="preserve">    Karşılıklar</v>
       </c>
       <c r="B25">
+        <v>86598059</v>
+      </c>
+      <c r="C25">
+        <v>97865084</v>
+      </c>
+      <c r="D25">
         <v>39724249</v>
       </c>
-      <c r="C25">
+      <c r="E25">
         <v>28663290</v>
       </c>
-      <c r="D25">
+      <c r="F25">
         <v>26610986</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>67860321</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>66758349</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>11639509</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>11243467</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>6312238</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>5872408</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <v>4408943</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>2620032</v>
       </c>
     </row>
@@ -1232,33 +1373,39 @@
         <v xml:space="preserve">    Cari Vergi Borcu</v>
       </c>
       <c r="B26">
+        <v>1103356862</v>
+      </c>
+      <c r="C26">
+        <v>916961037</v>
+      </c>
+      <c r="D26">
         <v>778658225</v>
       </c>
-      <c r="C26">
+      <c r="E26">
         <v>501327424</v>
       </c>
-      <c r="D26">
+      <c r="F26">
         <v>544126231</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>292415152</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>152830332</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>156623981</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>61441681</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>80486026</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>36302144</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>2082023</v>
       </c>
     </row>
@@ -1267,36 +1414,42 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Borcu</v>
       </c>
       <c r="B27">
+        <v>1995589335</v>
+      </c>
+      <c r="C27">
+        <v>1722145314</v>
+      </c>
+      <c r="D27">
         <v>1304223738</v>
       </c>
-      <c r="C27">
+      <c r="E27">
         <v>1123582313</v>
       </c>
-      <c r="D27">
+      <c r="F27">
         <v>975320144</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>929026496</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>882800880</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>203027124</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>364695148</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>177713537</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>149639548</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>69233913</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>43067085</v>
       </c>
     </row>
@@ -1305,36 +1458,42 @@
         <v xml:space="preserve">    Diğer Yükümlülükler</v>
       </c>
       <c r="B28">
+        <v>3552660781</v>
+      </c>
+      <c r="C28">
+        <v>3389960026</v>
+      </c>
+      <c r="D28">
         <v>1611207783</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>774602924</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>1024748866</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>1604112842</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>1683716540</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>84467643</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>216597989</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>62286694</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>50896937</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>33992079</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>24179707</v>
       </c>
     </row>
@@ -1343,36 +1502,42 @@
         <v xml:space="preserve">    (ARA TOPLAM) 2</v>
       </c>
       <c r="B29">
+        <v>40860172861</v>
+      </c>
+      <c r="C29">
+        <v>34999489997</v>
+      </c>
+      <c r="D29">
         <v>25935450639</v>
       </c>
-      <c r="C29">
+      <c r="E29">
         <v>17685953327</v>
       </c>
-      <c r="D29">
+      <c r="F29">
         <v>13781734492</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>14828567715</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>12245365598</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>4037994821</v>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>3157367721</v>
       </c>
-      <c r="I29">
+      <c r="K29">
         <v>2272240043</v>
       </c>
-      <c r="J29">
+      <c r="L29">
         <v>1384088856</v>
       </c>
-      <c r="K29">
+      <c r="M29">
         <v>977526113</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>720022048</v>
       </c>
     </row>
@@ -1383,25 +1548,28 @@
       <c r="B30">
         <v>0</v>
       </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
       <c r="D30">
         <v>0</v>
       </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
       <c r="F30">
         <v>0</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
       <c r="H30">
         <v>0</v>
       </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
       <c r="J30">
         <v>0</v>
       </c>
-      <c r="K30">
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>0</v>
       </c>
     </row>
@@ -1410,36 +1578,42 @@
         <v xml:space="preserve">    ÖZKAYNAKLAR</v>
       </c>
       <c r="B31">
+        <v>15819301983</v>
+      </c>
+      <c r="C31">
+        <v>12456487203</v>
+      </c>
+      <c r="D31">
         <v>9044897767</v>
       </c>
-      <c r="C31">
+      <c r="E31">
         <v>6566548206</v>
       </c>
-      <c r="D31">
+      <c r="F31">
         <v>5050243464</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>4086384065</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>3384288885</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>1616863997</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>1588401147</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>1163747262</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>784157490</v>
       </c>
-      <c r="K31">
+      <c r="M31">
         <v>786894588</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>281222370</v>
       </c>
     </row>
@@ -1454,10 +1628,10 @@
         <v>2070000000</v>
       </c>
       <c r="D32">
-        <v>180000000</v>
+        <v>2070000000</v>
       </c>
       <c r="E32">
-        <v>180000000</v>
+        <v>2070000000</v>
       </c>
       <c r="F32">
         <v>180000000</v>
@@ -1478,6 +1652,12 @@
         <v>180000000</v>
       </c>
       <c r="L32">
+        <v>180000000</v>
+      </c>
+      <c r="M32">
+        <v>180000000</v>
+      </c>
+      <c r="N32">
         <v>150000000</v>
       </c>
     </row>
@@ -1486,36 +1666,42 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler veya Giderler</v>
       </c>
       <c r="B33">
+        <v>-26436410</v>
+      </c>
+      <c r="C33">
+        <v>-19884813</v>
+      </c>
+      <c r="D33">
         <v>-17137360</v>
       </c>
-      <c r="C33">
+      <c r="E33">
         <v>-13809538</v>
       </c>
-      <c r="D33">
+      <c r="F33">
         <v>-10918665</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>-14099221</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>-8444787</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>-5594755</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>-4181332</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>-3266881</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>-2558349</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <v>-2310054</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>-399875</v>
       </c>
     </row>
@@ -1524,36 +1710,42 @@
         <v xml:space="preserve">    Kar Yedekleri</v>
       </c>
       <c r="B34">
+        <v>464839411</v>
+      </c>
+      <c r="C34">
+        <v>153597609</v>
+      </c>
+      <c r="D34">
         <v>133038966</v>
       </c>
-      <c r="C34">
+      <c r="E34">
         <v>115705406</v>
       </c>
-      <c r="D34">
+      <c r="F34">
         <v>103052395</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>52460396</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>42339623</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>35234916</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>31360154</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>10837898</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>7698688</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>5286812</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>2743574</v>
       </c>
     </row>
@@ -1562,36 +1754,42 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar veya Zararı</v>
       </c>
       <c r="B35">
-        <v>513082384</v>
+        <v>8838548255</v>
       </c>
       <c r="C35">
         <v>513082384</v>
       </c>
       <c r="D35">
+        <v>513082384</v>
+      </c>
+      <c r="E35">
+        <v>513082384</v>
+      </c>
+      <c r="F35">
         <v>2251082384</v>
       </c>
-      <c r="E35">
+      <c r="G35">
         <v>221138248</v>
-      </c>
-      <c r="F35">
-        <v>568262718</v>
-      </c>
-      <c r="G35">
-        <v>568262719</v>
       </c>
       <c r="H35">
         <v>568262718</v>
       </c>
       <c r="I35">
-        <v>128878671</v>
+        <v>568262719</v>
       </c>
       <c r="J35">
-        <v>128878671</v>
+        <v>568262718</v>
       </c>
       <c r="K35">
         <v>128878671</v>
       </c>
       <c r="L35">
+        <v>128878671</v>
+      </c>
+      <c r="M35">
+        <v>128878671</v>
+      </c>
+      <c r="N35">
         <v>13353002</v>
       </c>
     </row>
@@ -1600,36 +1798,42 @@
         <v xml:space="preserve">    Dönem Net Karı veya Zararı</v>
       </c>
       <c r="B36">
+        <v>3361411828</v>
+      </c>
+      <c r="C36">
+        <v>8620499737</v>
+      </c>
+      <c r="D36">
         <v>5285530688</v>
       </c>
-      <c r="C36">
+      <c r="E36">
         <v>2819599711</v>
       </c>
-      <c r="D36">
+      <c r="F36">
         <v>1108873122</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>2159865716</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1191350824</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>732216457</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>706214947</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>750182993</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>312916736</v>
       </c>
-      <c r="K36">
+      <c r="M36">
         <v>115193528</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>115525669</v>
       </c>
     </row>
@@ -1638,18 +1842,24 @@
         <v xml:space="preserve">    Kontrol Gücü Olmayan Paylar</v>
       </c>
       <c r="B37">
+        <v>1065627185</v>
+      </c>
+      <c r="C37">
+        <v>1073880572</v>
+      </c>
+      <c r="D37">
         <v>1015071375</v>
       </c>
-      <c r="C37">
+      <c r="E37">
         <v>1016658529</v>
       </c>
-      <c r="D37">
+      <c r="F37">
         <v>1022842514</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>1091707212</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>1015468794</v>
       </c>
     </row>
@@ -1658,36 +1868,42 @@
         <v xml:space="preserve">    TOPLAM KAYNAKLAR</v>
       </c>
       <c r="B38">
+        <v>56679474844</v>
+      </c>
+      <c r="C38">
+        <v>47455977200</v>
+      </c>
+      <c r="D38">
         <v>34980348406</v>
       </c>
-      <c r="C38">
+      <c r="E38">
         <v>24252501533</v>
       </c>
-      <c r="D38">
+      <c r="F38">
         <v>18831977956</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>18914951780</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>15629654483</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>5654858818</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>4745768868</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>3435987305</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>2168246346</v>
       </c>
-      <c r="K38">
+      <c r="M38">
         <v>1764420701</v>
       </c>
-      <c r="L38">
+      <c r="N38">
         <v>1001244418</v>
       </c>
     </row>
@@ -1696,27 +1912,33 @@
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
       <c r="C39">
+        <v>-13032599</v>
+      </c>
+      <c r="D39">
+        <v>-166774501</v>
+      </c>
+      <c r="E39">
         <v>-685183138</v>
       </c>
-      <c r="D39">
+      <c r="F39">
         <v>-1490545550</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>-2589210225</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:R30"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -1732,6 +1954,8 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1739,48 +1963,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>2022/9</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>2022/3</v>
       </c>
     </row>
@@ -1794,48 +2024,54 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>4032758951</v>
+      </c>
+      <c r="C3">
+        <v>14649868053</v>
+      </c>
+      <c r="D3">
         <v>9414007955</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>5683599350</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>2887407380</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>5118426039</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>2925079762</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>1516181456</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>685097857</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>1347661079</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>803461177</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>363028158</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>166510757</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>461860415</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>254209355</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>176433511</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>87635691</v>
       </c>
     </row>
@@ -1849,6 +2085,9 @@
       <c r="C4">
         <v>0</v>
       </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
       <c r="E4">
         <v>0</v>
       </c>
@@ -1873,6 +2112,9 @@
       <c r="C7">
         <v>0</v>
       </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
       <c r="E7">
         <v>0</v>
       </c>
@@ -1887,7 +2129,13 @@
       <c r="C8">
         <v>0</v>
       </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
       <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>153877579</v>
       </c>
     </row>
@@ -1896,48 +2144,54 @@
         <v xml:space="preserve">    Tasarruf Finansman Gelirleri</v>
       </c>
       <c r="B9">
+        <v>4032758951</v>
+      </c>
+      <c r="C9">
+        <v>14649868053</v>
+      </c>
+      <c r="D9">
         <v>9414007955</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>5683599350</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>2887407380</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>4964548460</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>2925079762</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>1516181456</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>685097857</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>1347661079</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>803461177</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>363028158</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>166510757</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>461860415</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>254209355</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>176433511</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>87635691</v>
       </c>
     </row>
@@ -1946,48 +2200,54 @@
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-22177137</v>
+      </c>
+      <c r="C10">
+        <v>-193583342</v>
+      </c>
+      <c r="D10">
         <v>-147633010</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>-131250845</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>-91948720</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-218090212</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>-117337688</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>-14108527</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-6596436</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-25535235</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>-8926768</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-6163550</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-2623792</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>-13994921</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>-9444201</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>-4065923</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>-1505696</v>
       </c>
     </row>
@@ -1996,48 +2256,54 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>4010581814</v>
+      </c>
+      <c r="C11">
+        <v>14456284711</v>
+      </c>
+      <c r="D11">
         <v>9266374945</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>5552348505</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>2795458660</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>4900335827</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>2807742074</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>1502072929</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>678501421</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>1322125844</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>794534409</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>356864608</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>163886965</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>447865494</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>244765154</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>172367588</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>86129995</v>
       </c>
     </row>
@@ -2046,48 +2312,54 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-1725631994</v>
+      </c>
+      <c r="C12">
+        <v>-4876333996</v>
+      </c>
+      <c r="D12">
         <v>-3193824122</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>-2162090000</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>-1228681978</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>-2126395308</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>-1402497089</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>-610071756</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-281559138</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-621760692</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>-413238054</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>-236971043</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>-124140654</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>-309101861</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>-207945247</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>-129794828</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>-57277039</v>
       </c>
     </row>
@@ -2096,48 +2368,54 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>2284949820</v>
+      </c>
+      <c r="C13">
+        <v>9579950715</v>
+      </c>
+      <c r="D13">
         <v>6072550823</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>3390258505</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>1566776682</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>2773940519</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>1405244985</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>892001173</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>396942283</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>700365152</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>381296355</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>119893565</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>39746311</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>138763633</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>36819907</v>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>42572760</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>28852956</v>
       </c>
     </row>
@@ -2146,48 +2424,54 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>2511828262</v>
+      </c>
+      <c r="C14">
+        <v>3054641185</v>
+      </c>
+      <c r="D14">
         <v>1771923185</v>
       </c>
-      <c r="C14">
+      <c r="E14">
         <v>997529418</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>405008972</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>536622568</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>306762149</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>103538816</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>564089906</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>305027055</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>77209137</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>23571834</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>3891341</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>8306586</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>2984078</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
         <v>1426278</v>
       </c>
-      <c r="P14">
+      <c r="R14">
         <v>2642124</v>
       </c>
     </row>
@@ -2196,48 +2480,54 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-17718702</v>
+      </c>
+      <c r="C15">
+        <v>-47813799</v>
+      </c>
+      <c r="D15">
         <v>-8956074</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-7497918</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>-6497871</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>-14133041</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-8995041</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-126822</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-2008788</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>455617</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>766077</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>915803</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>538843</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>264379</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>-1252094</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>-755143</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>0</v>
       </c>
     </row>
@@ -2246,39 +2536,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-15784794</v>
+      </c>
+      <c r="C16">
+        <v>-262449278</v>
+      </c>
+      <c r="D16">
         <v>-254120113</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-241530260</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>-210956163</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-221351958</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-61756371</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-12212164</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>0</v>
       </c>
       <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="P16">
         <v>-109008</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>-20807486</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>0</v>
       </c>
     </row>
@@ -2287,48 +2583,54 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>4763274586</v>
+      </c>
+      <c r="C17">
+        <v>12324328823</v>
+      </c>
+      <c r="D17">
         <v>7581397821</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>4138759745</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>1754331620</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>3075078088</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>1641255722</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>983201003</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>959023401</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>1005847824</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>459271569</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>144381202</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>44176495</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>147334598</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>38442883</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>22436409</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>31495080</v>
       </c>
     </row>
@@ -2342,6 +2644,9 @@
       <c r="C18">
         <v>0</v>
       </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
       <c r="E18">
         <v>0</v>
       </c>
@@ -2356,6 +2661,9 @@
       <c r="C19">
         <v>0</v>
       </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
       <c r="E19">
         <v>0</v>
       </c>
@@ -2370,6 +2678,9 @@
       <c r="C20">
         <v>0</v>
       </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
       <c r="E20">
         <v>0</v>
       </c>
@@ -2379,48 +2690,54 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>4763274586</v>
+      </c>
+      <c r="C21">
+        <v>12324328823</v>
+      </c>
+      <c r="D21">
         <v>7581397821</v>
       </c>
-      <c r="C21">
+      <c r="E21">
         <v>4138759745</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <v>1754331620</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>3075078088</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>1641255722</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>983201003</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>959023401</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>1005847824</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>459271569</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>144381202</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>44176495</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>147334598</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>38442883</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>22436409</v>
       </c>
-      <c r="P21">
+      <c r="R21">
         <v>31495080</v>
       </c>
     </row>
@@ -2429,48 +2746,54 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-1410116145</v>
+      </c>
+      <c r="C22">
+        <v>-3595180265</v>
+      </c>
+      <c r="D22">
         <v>-2238527509</v>
       </c>
-      <c r="C22">
+      <c r="E22">
         <v>-1260233256</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <v>-577847735</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>-854930068</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>-435198337</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>-250984546</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>-252808454</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>-255664831</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>-146354833</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>-29187674</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>-10090625</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>-31808929</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>-8864583</v>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>-5153166</v>
       </c>
-      <c r="P22">
+      <c r="R22">
         <v>-6632943</v>
       </c>
     </row>
@@ -2479,39 +2802,45 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-1134534968</v>
+      </c>
+      <c r="C23">
+        <v>-2741429866</v>
+      </c>
+      <c r="D23">
         <v>-1803876164</v>
       </c>
-      <c r="C23">
+      <c r="E23">
         <v>-1007649546</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>-474765140</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>-686639905</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>-379078542</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>-224673298</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>-65434935</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>-120301627</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>-39242751</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>-2543301</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>0</v>
       </c>
     </row>
@@ -2524,19 +2853,28 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gider Etkisi</v>
       </c>
-      <c r="E25">
+      <c r="B25">
+        <v>1912121</v>
+      </c>
+      <c r="C25">
+        <v>50839</v>
+      </c>
+      <c r="F25">
+        <v>1036927</v>
+      </c>
+      <c r="G25">
         <v>-186650496</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>16996833</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>-135363204</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>-31808929</v>
       </c>
-      <c r="N25">
+      <c r="P25">
         <v>0</v>
       </c>
     </row>
@@ -2545,48 +2883,54 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>3353158441</v>
+      </c>
+      <c r="C26">
+        <v>8729148558</v>
+      </c>
+      <c r="D26">
         <v>5342870312</v>
       </c>
-      <c r="C26">
+      <c r="E26">
         <v>2878526489</v>
       </c>
-      <c r="D26">
+      <c r="F26">
         <v>1176483885</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>2220148020</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1206057385</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>732216457</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>706214947</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>750182993</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>312916736</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>115193528</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>34085870</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>115525669</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>29578300</v>
       </c>
-      <c r="O26">
+      <c r="Q26">
         <v>17283243</v>
       </c>
-      <c r="P26">
+      <c r="R26">
         <v>24862137</v>
       </c>
     </row>
@@ -2600,6 +2944,9 @@
       <c r="C27">
         <v>0</v>
       </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
       <c r="E27">
         <v>0</v>
       </c>
@@ -2609,48 +2956,54 @@
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>3353158441</v>
+      </c>
+      <c r="C28">
+        <v>8729148558</v>
+      </c>
+      <c r="D28">
         <v>5342870312</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>2878526489</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>1176483885</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>2220148020</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>1206057385</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>732216457</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>706214947</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>750182993</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>312916736</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>115193528</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>34085870</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>115525669</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>29578300</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>17283243</v>
       </c>
-      <c r="P28">
+      <c r="R28">
         <v>24862137</v>
       </c>
     </row>
@@ -2659,30 +3012,36 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B29">
+        <v>-8253387</v>
+      </c>
+      <c r="C29">
+        <v>108648821</v>
+      </c>
+      <c r="D29">
         <v>57339624</v>
       </c>
-      <c r="C29">
+      <c r="E29">
         <v>58926778</v>
       </c>
-      <c r="D29">
+      <c r="F29">
         <v>67610763</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>60282304</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>14706561</v>
       </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
         <v>0</v>
       </c>
     </row>
@@ -2691,63 +3050,69 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>3361411828</v>
+      </c>
+      <c r="C30">
+        <v>8620499737</v>
+      </c>
+      <c r="D30">
         <v>5285530688</v>
       </c>
-      <c r="C30">
+      <c r="E30">
         <v>2819599711</v>
       </c>
-      <c r="D30">
+      <c r="F30">
         <v>1108873122</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>2159865716</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>1191350824</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>732216457</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>706214947</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>750182993</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>312916736</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <v>115193528</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>34085870</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>115525669</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>29578300</v>
       </c>
-      <c r="O30">
+      <c r="Q30">
         <v>17283243</v>
       </c>
-      <c r="P30">
+      <c r="R30">
         <v>24862137</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:R30"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -2763,6 +3128,8 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2770,48 +3137,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>2022/9</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>2022/3</v>
       </c>
     </row>
@@ -2825,48 +3198,54 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>4032758951</v>
+      </c>
+      <c r="C3">
+        <v>5235860098</v>
+      </c>
+      <c r="D3">
         <v>3730408605</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>2796191970</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>2887407380</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>2193346277</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1408898306</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>831083599</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>685097857</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>544199902</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>440433019</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>196517401</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>166510757</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>207651060</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>77775844</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>88797820</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>87635691</v>
       </c>
     </row>
@@ -2877,6 +3256,12 @@
       <c r="B4">
         <v>0</v>
       </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -2895,6 +3280,12 @@
       <c r="B7">
         <v>0</v>
       </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -2903,54 +3294,66 @@
       <c r="B8">
         <v>0</v>
       </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v xml:space="preserve">    Tasarruf Finansman Gelirleri</v>
       </c>
       <c r="B9">
+        <v>4032758951</v>
+      </c>
+      <c r="C9">
+        <v>5235860098</v>
+      </c>
+      <c r="D9">
         <v>3730408605</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>2796191970</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>2887407380</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>2039468698</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>1408898306</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>831083599</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>685097857</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>544199902</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>440433019</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>196517401</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>166510757</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>207651060</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>77775844</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>88797820</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>87635691</v>
       </c>
     </row>
@@ -2959,48 +3362,54 @@
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-22177137</v>
+      </c>
+      <c r="C10">
+        <v>-45950332</v>
+      </c>
+      <c r="D10">
         <v>-16382165</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>-39302125</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>-91948720</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-100752524</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>-103229161</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>-7512091</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-6596436</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-16608467</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>-2763218</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-3539758</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-2623792</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>-4550720</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>-5378278</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>-2560227</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>-1505696</v>
       </c>
     </row>
@@ -3009,48 +3418,54 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>4010581814</v>
+      </c>
+      <c r="C11">
+        <v>5189909766</v>
+      </c>
+      <c r="D11">
         <v>3714026440</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>2756889845</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>2795458660</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>2092593753</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>1305669145</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>823571508</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>678501421</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>527591435</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>437669801</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>192977643</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>163886965</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>203100340</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>72397566</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>86237593</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>86129995</v>
       </c>
     </row>
@@ -3059,48 +3474,54 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-1725631994</v>
+      </c>
+      <c r="C12">
+        <v>-1682509874</v>
+      </c>
+      <c r="D12">
         <v>-1031734122</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>-933408022</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>-1228681978</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>-723898219</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>-792425333</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>-328512618</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-281559138</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-208522638</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>-176267011</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>-112830389</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>-124140654</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>-101156614</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>-78150419</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>-72517789</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>-57277039</v>
       </c>
     </row>
@@ -3109,48 +3530,54 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>2284949820</v>
+      </c>
+      <c r="C13">
+        <v>3507399892</v>
+      </c>
+      <c r="D13">
         <v>2682292318</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>1823481823</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>1566776682</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>1368695534</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>513243812</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>495058890</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>396942283</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>319068797</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>261402790</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>80147254</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>39746311</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>101943726</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>-5752853</v>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>13719804</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>28852956</v>
       </c>
     </row>
@@ -3159,48 +3586,54 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>2511828262</v>
+      </c>
+      <c r="C14">
+        <v>1282718000</v>
+      </c>
+      <c r="D14">
         <v>774393767</v>
       </c>
-      <c r="C14">
+      <c r="E14">
         <v>592520446</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>405008972</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>229860419</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>203223333</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>-460551090</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>564089906</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>227817918</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>53637303</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>19680493</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>3891341</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>5322508</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>1557800</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
         <v>-1215846</v>
       </c>
-      <c r="P14">
+      <c r="R14">
         <v>2642124</v>
       </c>
     </row>
@@ -3209,48 +3642,54 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-17718702</v>
+      </c>
+      <c r="C15">
+        <v>-38857725</v>
+      </c>
+      <c r="D15">
         <v>-1458156</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-1000047</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>-6497871</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>-5138000</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-8868219</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>1881966</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-2008788</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-310460</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>-149726</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>376960</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>538843</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>1516473</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>-496951</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>-755143</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>0</v>
       </c>
     </row>
@@ -3259,39 +3698,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-15784794</v>
+      </c>
+      <c r="C16">
+        <v>-8329165</v>
+      </c>
+      <c r="D16">
         <v>-12589853</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-30574097</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>-210956163</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-159595587</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-49544207</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-12212164</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>0</v>
       </c>
       <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="P16">
         <v>20698478</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>-20807486</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>0</v>
       </c>
     </row>
@@ -3300,48 +3745,54 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>4763274586</v>
+      </c>
+      <c r="C17">
+        <v>4742931002</v>
+      </c>
+      <c r="D17">
         <v>3442638076</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>2384428125</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>1754331620</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>1433822366</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>658054719</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>24177602</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>959023401</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>546576255</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>314890367</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>100204707</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>44176495</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>108891715</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>16006474</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>-9058671</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>31495080</v>
       </c>
     </row>
@@ -3352,6 +3803,12 @@
       <c r="B18">
         <v>0</v>
       </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -3360,6 +3817,12 @@
       <c r="B19">
         <v>0</v>
       </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -3368,54 +3831,66 @@
       <c r="B20">
         <v>0</v>
       </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>4763274586</v>
+      </c>
+      <c r="C21">
+        <v>4742931002</v>
+      </c>
+      <c r="D21">
         <v>3442638076</v>
       </c>
-      <c r="C21">
+      <c r="E21">
         <v>2384428125</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <v>1754331620</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>1433822366</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>658054719</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>24177602</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>959023401</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>546576255</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>314890367</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>100204707</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>44176495</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>108891715</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>16006474</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>-9058671</v>
       </c>
-      <c r="P21">
+      <c r="R21">
         <v>31495080</v>
       </c>
     </row>
@@ -3424,48 +3899,54 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-1410116145</v>
+      </c>
+      <c r="C22">
+        <v>-1356652756</v>
+      </c>
+      <c r="D22">
         <v>-978294253</v>
       </c>
-      <c r="C22">
+      <c r="E22">
         <v>-682385521</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <v>-577847735</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>-419731731</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>-184213791</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>1823908</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>-252808454</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>-109309998</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>-117167159</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>-19097049</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>-10090625</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>-22944346</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>-3711417</v>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>1479777</v>
       </c>
-      <c r="P22">
+      <c r="R22">
         <v>-6632943</v>
       </c>
     </row>
@@ -3474,36 +3955,42 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-1134534968</v>
+      </c>
+      <c r="C23">
+        <v>-937553702</v>
+      </c>
+      <c r="D23">
         <v>-796226618</v>
       </c>
-      <c r="C23">
+      <c r="E23">
         <v>-532884406</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>-474765140</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>-307561363</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>-154405244</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>-159238363</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>-65434935</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>-81058876</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>-36699450</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>-2543301</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>0</v>
       </c>
     </row>
@@ -3516,10 +4003,16 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gider Etkisi</v>
       </c>
-      <c r="E25">
+      <c r="B25">
+        <v>1912121</v>
+      </c>
+      <c r="F25">
+        <v>1036927</v>
+      </c>
+      <c r="G25">
         <v>-203647329</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>-31808929</v>
       </c>
     </row>
@@ -3528,48 +4021,54 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>3353158441</v>
+      </c>
+      <c r="C26">
+        <v>3386278246</v>
+      </c>
+      <c r="D26">
         <v>2464343823</v>
       </c>
-      <c r="C26">
+      <c r="E26">
         <v>1702042604</v>
       </c>
-      <c r="D26">
+      <c r="F26">
         <v>1176483885</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>1014090635</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>473840928</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>26001510</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>706214947</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>437266257</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>197723208</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>81107658</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>34085870</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>85947369</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>12295057</v>
       </c>
-      <c r="O26">
+      <c r="Q26">
         <v>-7578894</v>
       </c>
-      <c r="P26">
+      <c r="R26">
         <v>24862137</v>
       </c>
     </row>
@@ -3580,54 +4079,66 @@
       <c r="B27">
         <v>0</v>
       </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>3353158441</v>
+      </c>
+      <c r="C28">
+        <v>3386278246</v>
+      </c>
+      <c r="D28">
         <v>2464343823</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>1702042604</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>1176483885</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>1014090635</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>473840928</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>26001510</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>706214947</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>437266257</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>197723208</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>81107658</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>34085870</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>85947369</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>12295057</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>-7578894</v>
       </c>
-      <c r="P28">
+      <c r="R28">
         <v>24862137</v>
       </c>
     </row>
@@ -3636,27 +4147,33 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B29">
+        <v>-8253387</v>
+      </c>
+      <c r="C29">
+        <v>51309197</v>
+      </c>
+      <c r="D29">
         <v>-1587154</v>
       </c>
-      <c r="C29">
+      <c r="E29">
         <v>-8683985</v>
       </c>
-      <c r="D29">
+      <c r="F29">
         <v>67610763</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>45575743</v>
       </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
         <v>0</v>
       </c>
     </row>
@@ -3665,63 +4182,69 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>3361411828</v>
+      </c>
+      <c r="C30">
+        <v>3334969049</v>
+      </c>
+      <c r="D30">
         <v>2465930977</v>
       </c>
-      <c r="C30">
+      <c r="E30">
         <v>1710726589</v>
       </c>
-      <c r="D30">
+      <c r="F30">
         <v>1108873122</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>968514892</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>459134367</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>26001510</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>706214947</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>437266257</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>197723208</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <v>81107658</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>34085870</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>85947369</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>12295057</v>
       </c>
-      <c r="O30">
+      <c r="Q30">
         <v>-7578894</v>
       </c>
-      <c r="P30">
+      <c r="R30">
         <v>24862137</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:R30"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -3737,6 +4260,8 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3744,48 +4269,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>2022/9</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>2022/3</v>
       </c>
     </row>
@@ -3799,39 +4330,45 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>15795219624</v>
+      </c>
+      <c r="C3">
+        <v>14649868053</v>
+      </c>
+      <c r="D3">
         <v>11607354232</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>9285843933</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>7320735562</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>5118426039</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>3469279664</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>2500814377</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>1866248179</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>1347661079</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>1011112237</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>648455062</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>540735481</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>461860415</v>
       </c>
     </row>
@@ -3839,7 +4376,7 @@
       <c r="A4" t="str">
         <v xml:space="preserve">    Faktoring Gelirleri</v>
       </c>
-      <c r="E4">
+      <c r="C4">
         <v>0</v>
       </c>
     </row>
@@ -3857,7 +4394,7 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Finansman Kredilerinden Gelirler</v>
       </c>
-      <c r="E7">
+      <c r="C7">
         <v>0</v>
       </c>
     </row>
@@ -3865,7 +4402,10 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Kiralama Gelirleri</v>
       </c>
-      <c r="E8">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>153877579</v>
       </c>
     </row>
@@ -3874,39 +4414,45 @@
         <v xml:space="preserve">    Tasarruf Finansman Gelirleri</v>
       </c>
       <c r="B9">
+        <v>15795219624</v>
+      </c>
+      <c r="C9">
+        <v>14649868053</v>
+      </c>
+      <c r="D9">
         <v>11453476653</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>9131966354</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>7166857983</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>4964548460</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>3469279664</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>2500814377</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>1866248179</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>1347661079</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>1011112237</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>648455062</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>540735481</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>461860415</v>
       </c>
     </row>
@@ -3915,39 +4461,45 @@
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-123811759</v>
+      </c>
+      <c r="C10">
+        <v>-193583342</v>
+      </c>
+      <c r="D10">
         <v>-248385534</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>-335232530</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>-303442496</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-218090212</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>-133946155</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>-33480212</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-29507879</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-25535235</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>-13477488</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-16092548</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-15113017</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>-13994921</v>
       </c>
     </row>
@@ -3956,39 +4508,45 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>15671407865</v>
+      </c>
+      <c r="C11">
+        <v>14456284711</v>
+      </c>
+      <c r="D11">
         <v>11358968698</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>8950611403</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>7017293066</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>4900335827</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>3335333509</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>2467334165</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>1836740300</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>1322125844</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>997634749</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>632362514</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>525622464</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>447865494</v>
       </c>
     </row>
@@ -3997,39 +4555,45 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-5373284012</v>
+      </c>
+      <c r="C12">
+        <v>-4876333996</v>
+      </c>
+      <c r="D12">
         <v>-3917722341</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>-3678413552</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>-3073518148</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>-2126395308</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>-1611019727</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>-994861405</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-779179176</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-621760692</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>-514394668</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>-416278076</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>-375965476</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>-309101861</v>
       </c>
     </row>
@@ -4038,39 +4602,45 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>10298123853</v>
+      </c>
+      <c r="C13">
+        <v>9579950715</v>
+      </c>
+      <c r="D13">
         <v>7441246357</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>5272197851</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>3943774918</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>2773940519</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>1724313782</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>1472472760</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>1057561124</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>700365152</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>483240081</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>216084438</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>149656988</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>138763633</v>
       </c>
     </row>
@@ -4079,39 +4649,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>5161460475</v>
+      </c>
+      <c r="C14">
+        <v>3054641185</v>
+      </c>
+      <c r="D14">
         <v>2001783604</v>
       </c>
-      <c r="C14">
+      <c r="E14">
         <v>1430613170</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>377541634</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>536622568</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>534580067</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>384994037</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>865225620</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>305027055</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>82531645</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>30452142</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>9555803</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>8306586</v>
       </c>
     </row>
@@ -4120,39 +4696,45 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-59034630</v>
+      </c>
+      <c r="C15">
+        <v>-47813799</v>
+      </c>
+      <c r="D15">
         <v>-14094074</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-21504137</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>-18622124</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>-14133041</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-9305501</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-587008</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-2092014</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>455617</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>2282550</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>1935325</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>803222</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>264379</v>
       </c>
     </row>
@@ -4161,15 +4743,21 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-67277909</v>
+      </c>
+      <c r="C16">
+        <v>-262449278</v>
+      </c>
+      <c r="D16">
         <v>-413715700</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-450670054</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>-432308121</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-221351958</v>
       </c>
     </row>
@@ -4178,39 +4766,45 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>15333271789</v>
+      </c>
+      <c r="C17">
+        <v>12324328823</v>
+      </c>
+      <c r="D17">
         <v>9015220187</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>6230636830</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>3870386307</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>3075078088</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>2187831977</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>1844667625</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>1920694730</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>1005847824</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>568163284</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>269279391</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>160016013</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>147334598</v>
       </c>
     </row>
@@ -4218,7 +4812,7 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Birleşme İşlemi Sonrasında Gelir Olarak Kaydedilen Fazlalık Tutarı</v>
       </c>
-      <c r="E18">
+      <c r="C18">
         <v>0</v>
       </c>
     </row>
@@ -4226,7 +4820,7 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemi Uygulanan Ortaklıklardan Kar (Zarar)</v>
       </c>
-      <c r="E19">
+      <c r="C19">
         <v>0</v>
       </c>
     </row>
@@ -4234,7 +4828,7 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Karı (Zararı)</v>
       </c>
-      <c r="E20">
+      <c r="C20">
         <v>0</v>
       </c>
     </row>
@@ -4243,39 +4837,45 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>15333271789</v>
+      </c>
+      <c r="C21">
+        <v>12324328823</v>
+      </c>
+      <c r="D21">
         <v>9015220187</v>
       </c>
-      <c r="C21">
+      <c r="E21">
         <v>6230636830</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <v>3870386307</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>3075078088</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>2187831977</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>1844667625</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>1920694730</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>1005847824</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>568163284</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>269279391</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>160016013</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>147334598</v>
       </c>
     </row>
@@ -4284,39 +4884,45 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-4427448675</v>
+      </c>
+      <c r="C22">
+        <v>-3595180265</v>
+      </c>
+      <c r="D22">
         <v>-2658259240</v>
       </c>
-      <c r="C22">
+      <c r="E22">
         <v>-1864178778</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <v>-1179969349</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>-854930068</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>-544508335</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>-477461703</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>-498382660</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>-255664831</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>-169299179</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>-55843437</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>-35266611</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>-31808929</v>
       </c>
     </row>
@@ -4325,30 +4931,36 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-3401199694</v>
+      </c>
+      <c r="C23">
+        <v>-2741429866</v>
+      </c>
+      <c r="D23">
         <v>-2111437527</v>
       </c>
-      <c r="C23">
+      <c r="E23">
         <v>-1469616153</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>-1095970110</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>-686639905</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>-460137418</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>-342431624</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>-185736562</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>-120301627</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>0</v>
       </c>
     </row>
@@ -4361,13 +4973,19 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gider Etkisi</v>
       </c>
-      <c r="E25">
+      <c r="B25">
+        <v>926033</v>
+      </c>
+      <c r="C25">
+        <v>50839</v>
+      </c>
+      <c r="G25">
         <v>-186650496</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>-135363204</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>-31808929</v>
       </c>
     </row>
@@ -4376,39 +4994,45 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>10905823114</v>
+      </c>
+      <c r="C26">
+        <v>8729148558</v>
+      </c>
+      <c r="D26">
         <v>6356960947</v>
       </c>
-      <c r="C26">
+      <c r="E26">
         <v>4366458052</v>
       </c>
-      <c r="D26">
+      <c r="F26">
         <v>2690416958</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>2220148020</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1643323642</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>1367205922</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>1422312070</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>750182993</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>398864105</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>213435954</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>124749402</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>115525669</v>
       </c>
     </row>
@@ -4416,7 +5040,7 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Net Karı (Zararı)</v>
       </c>
-      <c r="E27">
+      <c r="C27">
         <v>0</v>
       </c>
     </row>
@@ -4425,39 +5049,45 @@
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>10905823114</v>
+      </c>
+      <c r="C28">
+        <v>8729148558</v>
+      </c>
+      <c r="D28">
         <v>6356960947</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>4366458052</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>2690416958</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>2220148020</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>1643323642</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>1367205922</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>1422312070</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>750182993</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>398864105</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>213435954</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>124749402</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>115525669</v>
       </c>
     </row>
@@ -4466,9 +5096,15 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B29">
+        <v>32784671</v>
+      </c>
+      <c r="C29">
+        <v>108648821</v>
+      </c>
+      <c r="D29">
         <v>102915367</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>60282304</v>
       </c>
     </row>
@@ -4477,54 +5113,60 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>10873038443</v>
+      </c>
+      <c r="C30">
+        <v>8620499737</v>
+      </c>
+      <c r="D30">
         <v>6254045580</v>
       </c>
-      <c r="C30">
+      <c r="E30">
         <v>4247248970</v>
       </c>
-      <c r="D30">
+      <c r="F30">
         <v>2562523891</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>2159865716</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>1628617081</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>1367205922</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>1422312070</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>750182993</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>398864105</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <v>213435954</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>124749402</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>115525669</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:R45"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -4540,6 +5182,8 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4547,48 +5191,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>2022/9</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>2022/3</v>
       </c>
     </row>
@@ -4602,48 +5252,54 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>1549370953</v>
+      </c>
+      <c r="C3">
+        <v>8148201300</v>
+      </c>
+      <c r="D3">
         <v>4984933560</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>2712825300</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>1248902364</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>2421054361</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1261956675</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>840207681</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>208620067</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>925032202</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>399018966</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>148431990</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>49770420</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>168412573</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>65140399</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>25139656</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>34818307</v>
       </c>
     </row>
@@ -4652,42 +5308,48 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>63484350</v>
+      </c>
+      <c r="C4">
+        <v>485878994</v>
+      </c>
+      <c r="D4">
         <v>414005464</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>344647842</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>135176254</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>353383849</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>105839320</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>60470248</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>31568435</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>22481300</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>18533857</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>10140484</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>2646514</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>1341546</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>28767</v>
       </c>
     </row>
@@ -4696,39 +5358,45 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-30860</v>
+      </c>
+      <c r="C5">
+        <v>-96709174</v>
+      </c>
+      <c r="D5">
         <v>-101707836</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>-96075040</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>-68058168</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>-138103011</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>-117337688</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>-44846</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>-44846</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>-43248</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>-42848</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>-471145</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>-860036</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>-250989</v>
       </c>
     </row>
@@ -4742,48 +5410,54 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>4032758951</v>
+      </c>
+      <c r="C7">
+        <v>14649868053</v>
+      </c>
+      <c r="D7">
         <v>9414007955</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>5683599350</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>2887407380</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>4964548460</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>2925079762</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>1516181456</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>685097857</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>1347661079</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>803461177</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>363028158</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>166510757</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>461860415</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>254209355</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>176433511</v>
       </c>
-      <c r="P7">
+      <c r="R7">
         <v>87635691</v>
       </c>
     </row>
@@ -4797,48 +5471,54 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-970341693</v>
+      </c>
+      <c r="C9">
+        <v>-2698447400</v>
+      </c>
+      <c r="D9">
         <v>-1876880480</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>-1210521234</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>-722233669</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>-1320338474</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>-827152179</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>-392427525</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>-183503924</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>-378066094</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>-240454086</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>-130985957</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>-64302931</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>-134522426</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>-89282423</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>-59063827</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>-24127307</v>
       </c>
     </row>
@@ -4847,48 +5527,54 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-950946970</v>
+      </c>
+      <c r="C10">
+        <v>-2154381366</v>
+      </c>
+      <c r="D10">
         <v>-1353952998</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>-833630971</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>-256708812</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-479944200</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>-309452810</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>-174846591</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-271852799</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-175178805</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>-110052689</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-27105651</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-10090625</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>-31808929</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>-8864583</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>-5153166</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>-6632943</v>
       </c>
     </row>
@@ -4897,48 +5583,54 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-790404483</v>
+      </c>
+      <c r="C11">
+        <v>-2471612750</v>
+      </c>
+      <c r="D11">
         <v>-1618876289</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>-1247049112</v>
       </c>
-      <c r="D11">
-        <v>-769653370</v>
-      </c>
-      <c r="E11">
+      <c r="F11">
+        <v>-769653369</v>
+      </c>
+      <c r="G11">
         <v>-1011758178</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>-614502734</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>-169169907</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>-52689502</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>108179568</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>-72424447</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>-66601796</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>-44950447</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>-127986888</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>-90061914</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>-86825873</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>-22085901</v>
       </c>
     </row>
@@ -4947,48 +5639,54 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>-4285323288</v>
+      </c>
+      <c r="C12">
+        <v>6777739265</v>
+      </c>
+      <c r="D12">
         <v>6847933814</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>2086432896</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>-876599238</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>5771253880</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>4767756207</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>79614671</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-389001558</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-166600639</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>-338771247</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>-344100146</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>30830445</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>72427581</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>44865685</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>-9560126</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>-347738</v>
       </c>
     </row>
@@ -5006,7 +5704,7 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Alacaklarda Net (Artış) Azalış</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>-18843858</v>
       </c>
     </row>
@@ -5015,48 +5713,54 @@
         <v xml:space="preserve">    Tasarruf Finansman Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B16">
+        <v>-8448714657</v>
+      </c>
+      <c r="C16">
+        <v>-13148977779</v>
+      </c>
+      <c r="D16">
         <v>-5098362811</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-1804357763</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>124086433</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-3548815066</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-1883024679</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-1032820156</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>-591490551</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>-514836177</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>-318941741</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>-192268758</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>-87363993</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>-170517468</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>-113861719</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>-77434990</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>280121912</v>
       </c>
     </row>
@@ -5065,48 +5769,54 @@
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-1248718674</v>
+      </c>
+      <c r="C17">
+        <v>278338656</v>
+      </c>
+      <c r="D17">
         <v>747592372</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>733825017</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>-1526110</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>1379594171</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>1173775783</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>-572979208</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-699152497</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-1120065360</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-644115336</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>-405026261</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>-27307046</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>-57627119</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>-32291600</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>-27145211</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>-517719995</v>
       </c>
     </row>
@@ -5114,7 +5824,7 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Faktoring Borçlarındaki Net Artış (Azalış)</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>-12728251</v>
       </c>
     </row>
@@ -5123,42 +5833,48 @@
         <v xml:space="preserve">    Tasarruf Fon Havuzundaki Net Artış (Azalış)</v>
       </c>
       <c r="B19">
+        <v>5282964429</v>
+      </c>
+      <c r="C19">
+        <v>17783442281</v>
+      </c>
+      <c r="D19">
         <v>11417628729</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>4196900223</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>-235779928</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>6696424390</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>4153351019</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>1653359804</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>572064131</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>1192283026</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>510066453</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>230382182</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>116118605</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>229098064</v>
       </c>
-      <c r="P19">
+      <c r="R19">
         <v>229634676</v>
       </c>
     </row>
@@ -5166,25 +5882,25 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>-16564788</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>-14116243</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>103003298</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>-8745819</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>38825545</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>-8963185</v>
       </c>
-      <c r="P20">
+      <c r="R20">
         <v>12673946</v>
       </c>
     </row>
@@ -5192,13 +5908,13 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Alınan Kredilerdeki Net Artış (Azalış)</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>35540942</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>157459108</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>99157360</v>
       </c>
     </row>
@@ -5206,7 +5922,7 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Vadesi Gelmiş Borçlarda Net Artış (Azalış)</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>24501296</v>
       </c>
     </row>
@@ -5215,45 +5931,51 @@
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>129145614</v>
+      </c>
+      <c r="C23">
+        <v>1864936107</v>
+      </c>
+      <c r="D23">
         <v>-218924476</v>
       </c>
-      <c r="C23">
+      <c r="E23">
         <v>-1039934581</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>-763379633</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>1244050385</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1323654084</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>48619019</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>343693602</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>173014574</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>133063235</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>38128698</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>32648559</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>9058600</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>4825900</v>
       </c>
-      <c r="P23">
+      <c r="R23">
         <v>-5058277</v>
       </c>
     </row>
@@ -5262,48 +5984,54 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>-2735952335</v>
+      </c>
+      <c r="C24">
+        <v>14925940565</v>
+      </c>
+      <c r="D24">
         <v>11832867374</v>
       </c>
-      <c r="C24">
+      <c r="E24">
         <v>4799258196</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <v>372303126</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>8192308241</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>6029712882</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>919822352</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>-180381491</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>758431563</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>60247719</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>-195668156</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>80600865</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>240840154</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>110006084</v>
       </c>
-      <c r="O24">
+      <c r="Q24">
         <v>15579530</v>
       </c>
-      <c r="P24">
+      <c r="R24">
         <v>34470569</v>
       </c>
     </row>
@@ -5311,13 +6039,13 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    İktisap Edilen İştirakler, Bağlı Ortaklıklar ve Birlikte Kontrol Edilen Ortaklıklar (İş Ortaklıkları)</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>-2802466048</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>-2486217798</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>-230000000</v>
       </c>
     </row>
@@ -5331,48 +6059,54 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-747865381</v>
+      </c>
+      <c r="C27">
+        <v>-8003699543</v>
+      </c>
+      <c r="D27">
         <v>-7569275679</v>
       </c>
-      <c r="C27">
+      <c r="E27">
         <v>-3115944873</v>
       </c>
-      <c r="D27">
+      <c r="F27">
         <v>-33221158</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>-2292244165</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>-873985463</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>-49416444</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>-27407299</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>-263814638</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>-105727872</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>-64935323</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>-38974736</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>-146540748</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>-63627450</v>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>-15709357</v>
       </c>
-      <c r="P27">
+      <c r="R27">
         <v>-24126165</v>
       </c>
     </row>
@@ -5380,9 +6114,6 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Elden Çıkarılan Menkul ve Gayrimenkuller</v>
       </c>
-      <c r="B28">
-        <v>641774417</v>
-      </c>
       <c r="C28">
         <v>641774417</v>
       </c>
@@ -5390,33 +6121,39 @@
         <v>641774417</v>
       </c>
       <c r="E28">
+        <v>641774417</v>
+      </c>
+      <c r="F28">
+        <v>641774417</v>
+      </c>
+      <c r="G28">
         <v>288567054</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>288567053</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>-107397</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>24962904</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>24941522</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>8841544</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>8841544</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>10433488</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>4723164</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>42209</v>
       </c>
     </row>
@@ -5444,10 +6181,10 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>35459975</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>514203850</v>
       </c>
     </row>
@@ -5456,48 +6193,54 @@
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>-747865381</v>
+      </c>
+      <c r="C34">
+        <v>-7394903962</v>
+      </c>
+      <c r="D34">
         <v>-6988538741</v>
       </c>
-      <c r="C34">
+      <c r="E34">
         <v>-2552541496</v>
       </c>
-      <c r="D34">
+      <c r="F34">
         <v>515029208</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>-4806143159</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>-3071636208</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>-244063866</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>486796551</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>-238851734</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>-80786350</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>-56093779</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>-30133192</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>-136107260</v>
       </c>
-      <c r="N34">
+      <c r="P34">
         <v>-58904286</v>
       </c>
-      <c r="O34">
+      <c r="Q34">
         <v>-15667148</v>
       </c>
-      <c r="P34">
+      <c r="R34">
         <v>-24126165</v>
       </c>
     </row>
@@ -5510,19 +6253,22 @@
       <c r="A36" t="str">
         <v xml:space="preserve">    Krediler ve İhraç Edilen Menkul Değerlerden Kaynaklanan Nakit Çıkışı</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>-925125572</v>
       </c>
-      <c r="C36">
+      <c r="D36">
+        <v>-925125572</v>
+      </c>
+      <c r="E36">
         <v>-663851088</v>
       </c>
-      <c r="D36">
+      <c r="F36">
         <v>-304429054</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>-1501732795</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-1229618792</v>
       </c>
     </row>
@@ -5535,22 +6281,25 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Temettü Ödemeleri</v>
       </c>
-      <c r="B38">
-        <v>-198000000</v>
-      </c>
       <c r="C38">
         <v>-198000000</v>
       </c>
+      <c r="D38">
+        <v>-198000000</v>
+      </c>
       <c r="E38">
+        <v>-198000000</v>
+      </c>
+      <c r="G38">
         <v>-284757731</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>-284757731</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>-284757730</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>-284757731</v>
       </c>
     </row>
@@ -5559,48 +6308,54 @@
         <v xml:space="preserve">    Kiralamaya İlişkin Ödemeler</v>
       </c>
       <c r="B39">
+        <v>-22146277</v>
+      </c>
+      <c r="C39">
+        <v>-96874168</v>
+      </c>
+      <c r="D39">
         <v>-45925174</v>
       </c>
-      <c r="C39">
+      <c r="E39">
         <v>-35175805</v>
       </c>
-      <c r="D39">
+      <c r="F39">
         <v>-23890553</v>
       </c>
-      <c r="E39">
-        <v>-79987201</v>
-      </c>
-      <c r="F39">
+      <c r="G39">
+        <v>-79987200</v>
+      </c>
+      <c r="H39">
         <v>-31060852</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>-14108527</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-6596436</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>-25490389</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>-8881922</v>
       </c>
-      <c r="K39">
+      <c r="M39">
         <v>-6120302</v>
       </c>
-      <c r="L39">
+      <c r="N39">
         <v>-2580944</v>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>-13523776</v>
       </c>
-      <c r="N39">
+      <c r="P39">
         <v>-8584165</v>
       </c>
-      <c r="O39">
+      <c r="Q39">
         <v>-3814934</v>
       </c>
-      <c r="P39">
+      <c r="R39">
         <v>-1505696</v>
       </c>
     </row>
@@ -5608,31 +6363,34 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="B40">
-        <v>-114500000</v>
-      </c>
       <c r="C40">
         <v>-114500000</v>
       </c>
       <c r="D40">
         <v>-114500000</v>
       </c>
-      <c r="I40">
-        <v>30000000</v>
-      </c>
-      <c r="J40">
-        <v>-172623887</v>
+      <c r="E40">
+        <v>-114500000</v>
+      </c>
+      <c r="F40">
+        <v>-114500000</v>
       </c>
       <c r="K40">
         <v>30000000</v>
       </c>
+      <c r="L40">
+        <v>-172623887</v>
+      </c>
       <c r="M40">
+        <v>30000000</v>
+      </c>
+      <c r="O40">
         <v>50000000</v>
       </c>
-      <c r="N40">
+      <c r="P40">
         <v>50000000</v>
       </c>
-      <c r="O40">
+      <c r="Q40">
         <v>43350000</v>
       </c>
     </row>
@@ -5641,48 +6399,54 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
+        <v>-22146277</v>
+      </c>
+      <c r="C41">
+        <v>-1334499740</v>
+      </c>
+      <c r="D41">
         <v>-1283550746</v>
       </c>
-      <c r="C41">
+      <c r="E41">
         <v>-1011526893</v>
       </c>
-      <c r="D41">
+      <c r="F41">
         <v>-442819607</v>
       </c>
-      <c r="E41">
-        <v>-1866477727</v>
-      </c>
-      <c r="F41">
+      <c r="G41">
+        <v>-1866477726</v>
+      </c>
+      <c r="H41">
         <v>-1545437375</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>-298866257</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>-291354167</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>101624192</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>178339822</v>
       </c>
-      <c r="K41">
+      <c r="M41">
         <v>383725329</v>
       </c>
-      <c r="L41">
+      <c r="N41">
         <v>-2580944</v>
       </c>
-      <c r="M41">
+      <c r="O41">
         <v>36476224</v>
       </c>
-      <c r="N41">
+      <c r="P41">
         <v>41415835</v>
       </c>
-      <c r="O41">
+      <c r="Q41">
         <v>39535066</v>
       </c>
-      <c r="P41">
+      <c r="R41">
         <v>-1505696</v>
       </c>
     </row>
@@ -5702,7 +6466,7 @@
       <c r="E42">
         <v>0</v>
       </c>
-      <c r="N42">
+      <c r="P42">
         <v>0</v>
       </c>
     </row>
@@ -5711,48 +6475,54 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
+        <v>-3505963993</v>
+      </c>
+      <c r="C43">
+        <v>6196536863</v>
+      </c>
+      <c r="D43">
         <v>3560777887</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>1235189807</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>444512727</v>
       </c>
-      <c r="E43">
-        <v>1519687355</v>
-      </c>
-      <c r="F43">
+      <c r="G43">
+        <v>1519687356</v>
+      </c>
+      <c r="H43">
         <v>1412639299</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>376892229</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>15060893</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>621204021</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>157801191</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <v>131963394</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>47886729</v>
       </c>
-      <c r="M43">
+      <c r="O43">
         <v>141209118</v>
       </c>
-      <c r="N43">
+      <c r="P43">
         <v>92517633</v>
       </c>
-      <c r="O43">
+      <c r="Q43">
         <v>39447448</v>
       </c>
-      <c r="P43">
+      <c r="R43">
         <v>8838708</v>
       </c>
     </row>
@@ -5768,16 +6538,16 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:R45"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -5793,6 +6563,8 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5800,48 +6572,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>2022/9</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>2022/3</v>
       </c>
     </row>
@@ -5855,48 +6633,54 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>1549370953</v>
+      </c>
+      <c r="C3">
+        <v>3163267740</v>
+      </c>
+      <c r="D3">
         <v>2272108260</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>1463922936</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>1248902364</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>1159097686</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>421748994</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>631587614</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>208620067</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>526013236</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>250586976</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>98661570</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>49770420</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>103272174</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>40000743</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>-9678651</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>34818307</v>
       </c>
     </row>
@@ -5905,39 +6689,45 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>63484350</v>
+      </c>
+      <c r="C4">
+        <v>71873530</v>
+      </c>
+      <c r="D4">
         <v>69357622</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>209471588</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>135176254</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>247544529</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>45369072</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>28901813</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>31568435</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>3947443</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>8393373</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>7493970</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>2646514</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>28767</v>
       </c>
     </row>
@@ -5946,33 +6736,39 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-30860</v>
+      </c>
+      <c r="C5">
+        <v>4998662</v>
+      </c>
+      <c r="D5">
         <v>-5632796</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>-28016872</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>-68058168</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>-20765323</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>-1598</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>-400</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>-42848</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>388891</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>-609047</v>
       </c>
     </row>
@@ -5986,48 +6782,54 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>4032758951</v>
+      </c>
+      <c r="C7">
+        <v>5235860098</v>
+      </c>
+      <c r="D7">
         <v>3730408605</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>2796191970</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>2887407380</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>2039468698</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>1408898306</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>831083599</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>685097857</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>544199902</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>440433019</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>196517401</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>166510757</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>207651060</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>77775844</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>88797820</v>
       </c>
-      <c r="P7">
+      <c r="R7">
         <v>87635691</v>
       </c>
     </row>
@@ -6041,48 +6843,54 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-970341693</v>
+      </c>
+      <c r="C9">
+        <v>-821566920</v>
+      </c>
+      <c r="D9">
         <v>-666359246</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>-488287565</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>-722233669</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>-493186295</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>-434724654</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>-208923601</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>-183503924</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>-137612008</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>-109468129</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>-66683026</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>-64302931</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>-45240003</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>-30218596</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>-34936520</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>-24127307</v>
       </c>
     </row>
@@ -6091,48 +6899,54 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-950946970</v>
+      </c>
+      <c r="C10">
+        <v>-800428368</v>
+      </c>
+      <c r="D10">
         <v>-520322027</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>-576922159</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>-256708812</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-170491390</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>-134606219</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>97006208</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-271852799</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-65126116</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>-82947038</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-17015026</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-10090625</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>-22944346</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>-3711417</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>1479777</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>-6632943</v>
       </c>
     </row>
@@ -6141,48 +6955,54 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-790404483</v>
+      </c>
+      <c r="C11">
+        <v>-852736461</v>
+      </c>
+      <c r="D11">
         <v>-371827177</v>
       </c>
-      <c r="C11">
-        <v>-477395742</v>
-      </c>
-      <c r="D11">
-        <v>-769653370</v>
-      </c>
       <c r="E11">
+        <v>-477395743</v>
+      </c>
+      <c r="F11">
+        <v>-769653369</v>
+      </c>
+      <c r="G11">
         <v>-397255444</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>-445332827</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>-116480405</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>-52689502</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>180604015</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>-5822651</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>-21651349</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>-44950447</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>-37924974</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>-3236041</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>-64739972</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>-22085901</v>
       </c>
     </row>
@@ -6191,48 +7011,54 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>-4285323288</v>
+      </c>
+      <c r="C12">
+        <v>-70194549</v>
+      </c>
+      <c r="D12">
         <v>4761500918</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>2963032134</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>-876599238</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>1003497673</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>4688141536</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>468616229</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-389001558</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>172170608</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>5328899</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>-374930591</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>30830445</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>27561896</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>54425811</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>-9212388</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>-347738</v>
       </c>
     </row>
@@ -6256,48 +7082,54 @@
         <v xml:space="preserve">    Tasarruf Finansman Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B16">
+        <v>-8448714657</v>
+      </c>
+      <c r="C16">
+        <v>-8050614968</v>
+      </c>
+      <c r="D16">
         <v>-3294005048</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-1928444196</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>124086433</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-1665790387</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-850204523</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-441329605</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>-591490551</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>-195894436</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>-126672983</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>-104904765</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>-87363993</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>-56655749</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>-36426729</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>-357556902</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>280121912</v>
       </c>
     </row>
@@ -6306,48 +7138,54 @@
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-1248718674</v>
+      </c>
+      <c r="C17">
+        <v>-469253716</v>
+      </c>
+      <c r="D17">
         <v>13767355</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>735351127</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>-1526110</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>205818388</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>1746754991</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>126173289</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-699152497</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-475950024</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-239089075</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>-377719215</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>-27307046</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>-25335519</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>-5146389</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>490574784</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>-517719995</v>
       </c>
     </row>
@@ -6361,39 +7199,45 @@
         <v xml:space="preserve">    Tasarruf Fon Havuzundaki Net Artış (Azalış)</v>
       </c>
       <c r="B19">
+        <v>5282964429</v>
+      </c>
+      <c r="C19">
+        <v>6365813552</v>
+      </c>
+      <c r="D19">
         <v>7220728506</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>4432680151</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>-235779928</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>2543073371</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>2499991215</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>1081295673</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>572064131</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>682216573</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>279684271</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>114263577</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>116118605</v>
       </c>
-      <c r="P19">
+      <c r="R19">
         <v>229634676</v>
       </c>
     </row>
@@ -6401,19 +7245,19 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>-2448545</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>-14116243</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>-8745819</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>-21637131</v>
       </c>
-      <c r="P20">
+      <c r="R20">
         <v>12673946</v>
       </c>
     </row>
@@ -6421,7 +7265,7 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Alınan Kredilerdeki Net Artış (Azalış)</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>58301748</v>
       </c>
     </row>
@@ -6435,42 +7279,48 @@
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>129145614</v>
+      </c>
+      <c r="C23">
+        <v>2083860583</v>
+      </c>
+      <c r="D23">
         <v>821010105</v>
       </c>
-      <c r="C23">
+      <c r="E23">
         <v>-276554948</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>-763379633</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>-79603699</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1275035065</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>-295074583</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>343693602</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>39951339</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>38128698</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>23589959</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>4232700</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>9884177</v>
       </c>
-      <c r="P23">
+      <c r="R23">
         <v>-5058277</v>
       </c>
     </row>
@@ -6479,48 +7329,54 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>-2735952335</v>
+      </c>
+      <c r="C24">
+        <v>3093073191</v>
+      </c>
+      <c r="D24">
         <v>7033609178</v>
       </c>
-      <c r="C24">
+      <c r="E24">
         <v>4426955070</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <v>372303126</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>2162595359</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>5109890530</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>1100203843</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>-180381491</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>698183844</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>255915875</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>-276269021</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>80600865</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>130834070</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>94426554</v>
       </c>
-      <c r="O24">
+      <c r="Q24">
         <v>-18891039</v>
       </c>
-      <c r="P24">
+      <c r="R24">
         <v>34470569</v>
       </c>
     </row>
@@ -6528,10 +7384,10 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    İktisap Edilen İştirakler, Bağlı Ortaklıklar ve Birlikte Kontrol Edilen Ortaklıklar (İş Ortaklıkları)</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>-316248250</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>-2256217798</v>
       </c>
     </row>
@@ -6545,48 +7401,54 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-747865381</v>
+      </c>
+      <c r="C27">
+        <v>-434423864</v>
+      </c>
+      <c r="D27">
         <v>-4453330806</v>
       </c>
-      <c r="C27">
+      <c r="E27">
         <v>-3082723715</v>
       </c>
-      <c r="D27">
+      <c r="F27">
         <v>-33221158</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>-1418258702</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>-824569019</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>-22009145</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>-27407299</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>-158086766</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>-40792549</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>-25960587</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>-38974736</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>-82913298</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>-47918093</v>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>8416808</v>
       </c>
-      <c r="P27">
+      <c r="R27">
         <v>-24126165</v>
       </c>
     </row>
@@ -6594,37 +7456,40 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Elden Çıkarılan Menkul ve Gayrimenkuller</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>641774417</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>1</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>288674450</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>21382</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>16099978</v>
       </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
         <v>8841544</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>5710324</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>4680955</v>
       </c>
     </row>
@@ -6652,10 +7517,10 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>-478743875</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>514203850</v>
       </c>
     </row>
@@ -6664,48 +7529,54 @@
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>-747865381</v>
+      </c>
+      <c r="C34">
+        <v>-406365221</v>
+      </c>
+      <c r="D34">
         <v>-4435997245</v>
       </c>
-      <c r="C34">
+      <c r="E34">
         <v>-3067570704</v>
       </c>
-      <c r="D34">
+      <c r="F34">
         <v>515029208</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>-1734506951</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>-2827572342</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>-730860417</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>486796551</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>-158065384</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>-24692571</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>-25960587</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>-30133192</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>-77202974</v>
       </c>
-      <c r="N34">
+      <c r="P34">
         <v>-43237138</v>
       </c>
-      <c r="O34">
+      <c r="Q34">
         <v>8459017</v>
       </c>
-      <c r="P34">
+      <c r="R34">
         <v>-24126165</v>
       </c>
     </row>
@@ -6718,16 +7589,19 @@
       <c r="A36" t="str">
         <v xml:space="preserve">    Krediler ve İhraç Edilen Menkul Değerlerden Kaynaklanan Nakit Çıkışı</v>
       </c>
-      <c r="B36">
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
         <v>-261274484</v>
       </c>
-      <c r="C36">
+      <c r="E36">
         <v>-359422034</v>
       </c>
-      <c r="D36">
+      <c r="F36">
         <v>-304429054</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>-272114003</v>
       </c>
     </row>
@@ -6740,19 +7614,22 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Temettü Ödemeleri</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>-1</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>1</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>-284757731</v>
       </c>
     </row>
@@ -6761,48 +7638,54 @@
         <v xml:space="preserve">    Kiralamaya İlişkin Ödemeler</v>
       </c>
       <c r="B39">
+        <v>-22146277</v>
+      </c>
+      <c r="C39">
+        <v>-50948994</v>
+      </c>
+      <c r="D39">
         <v>-10749369</v>
       </c>
-      <c r="C39">
+      <c r="E39">
         <v>-11285252</v>
       </c>
-      <c r="D39">
+      <c r="F39">
         <v>-23890553</v>
       </c>
-      <c r="E39">
-        <v>-48926349</v>
-      </c>
-      <c r="F39">
+      <c r="G39">
+        <v>-48926348</v>
+      </c>
+      <c r="H39">
         <v>-16952325</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>-7512091</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-6596436</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>-16608467</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>-2761620</v>
       </c>
-      <c r="K39">
+      <c r="M39">
         <v>-3539358</v>
       </c>
-      <c r="L39">
+      <c r="N39">
         <v>-2580944</v>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>-4939611</v>
       </c>
-      <c r="N39">
+      <c r="P39">
         <v>-4769231</v>
       </c>
-      <c r="O39">
+      <c r="Q39">
         <v>-2309238</v>
       </c>
-      <c r="P39">
+      <c r="R39">
         <v>-1505696</v>
       </c>
     </row>
@@ -6810,25 +7693,28 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>-114500000</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>202623887</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>-202623887</v>
       </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
         <v>6650000</v>
       </c>
     </row>
@@ -6837,48 +7723,54 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
+        <v>-22146277</v>
+      </c>
+      <c r="C41">
+        <v>-50948994</v>
+      </c>
+      <c r="D41">
         <v>-272023853</v>
       </c>
-      <c r="C41">
+      <c r="E41">
         <v>-568707286</v>
       </c>
-      <c r="D41">
+      <c r="F41">
         <v>-442819607</v>
       </c>
-      <c r="E41">
-        <v>-321040352</v>
-      </c>
-      <c r="F41">
+      <c r="G41">
+        <v>-321040351</v>
+      </c>
+      <c r="H41">
         <v>-1246571118</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>-7512090</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>-291354167</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>-76715630</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>-205385507</v>
       </c>
-      <c r="K41">
+      <c r="M41">
         <v>386306273</v>
       </c>
-      <c r="L41">
+      <c r="N41">
         <v>-2580944</v>
       </c>
-      <c r="M41">
+      <c r="O41">
         <v>-4939611</v>
       </c>
-      <c r="N41">
+      <c r="P41">
         <v>1880769</v>
       </c>
-      <c r="O41">
+      <c r="Q41">
         <v>41040762</v>
       </c>
-      <c r="P41">
+      <c r="R41">
         <v>-1505696</v>
       </c>
     </row>
@@ -6901,48 +7793,54 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
+        <v>-3505963993</v>
+      </c>
+      <c r="C43">
+        <v>2635758976</v>
+      </c>
+      <c r="D43">
         <v>2325588080</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>790677080</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>444512727</v>
       </c>
-      <c r="E43">
-        <v>107048056</v>
-      </c>
-      <c r="F43">
+      <c r="G43">
+        <v>107048057</v>
+      </c>
+      <c r="H43">
         <v>1035747070</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>361831336</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>15060893</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>463402830</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>25837797</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <v>84076665</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>47886729</v>
       </c>
-      <c r="M43">
+      <c r="O43">
         <v>48691485</v>
       </c>
-      <c r="N43">
+      <c r="P43">
         <v>53070185</v>
       </c>
-      <c r="O43">
+      <c r="Q43">
         <v>30608740</v>
       </c>
-      <c r="P43">
+      <c r="R43">
         <v>8838708</v>
       </c>
     </row>
@@ -6958,16 +7856,16 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:R45"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -6983,6 +7881,8 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6990,48 +7890,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>2022/9</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>2022/3</v>
       </c>
     </row>
@@ -7045,39 +7951,45 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>8448669889</v>
+      </c>
+      <c r="C3">
+        <v>8148201300</v>
+      </c>
+      <c r="D3">
         <v>6144031246</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>4293671980</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>3461336658</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>2421054361</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1787969911</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>1616807893</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>1083881849</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>925032202</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>502291140</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>291704907</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>183364686</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>168412573</v>
       </c>
     </row>
@@ -7086,33 +7998,39 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>414187090</v>
+      </c>
+      <c r="C4">
+        <v>485878994</v>
+      </c>
+      <c r="D4">
         <v>661549993</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>637561443</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>456991668</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>353383849</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>109786763</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>72811064</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>51403221</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>22481300</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>3959293</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>1341546</v>
       </c>
     </row>
@@ -7121,24 +8039,30 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-28681866</v>
+      </c>
+      <c r="C5">
+        <v>-96709174</v>
+      </c>
+      <c r="D5">
         <v>-122473159</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>-138103011</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>-117337688</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>-44846</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>344045</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>-263404</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>-471145</v>
       </c>
     </row>
@@ -7152,39 +8076,45 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>15795219624</v>
+      </c>
+      <c r="C7">
+        <v>14649868053</v>
+      </c>
+      <c r="D7">
         <v>11453476653</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>9131966354</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>7166857983</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>4964548460</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>3469279664</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>2500814377</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>1866248179</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>1347661079</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>1011112237</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>648455062</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>540735481</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>461860415</v>
       </c>
     </row>
@@ -7198,39 +8128,45 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-2946555424</v>
+      </c>
+      <c r="C9">
+        <v>-2698447400</v>
+      </c>
+      <c r="D9">
         <v>-2370066775</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>-2138432183</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>-1859068219</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>-1320338474</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>-964764187</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>-639507662</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>-497267087</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>-378066094</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>-285694089</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>-206444556</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>-174698050</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>-134522426</v>
       </c>
     </row>
@@ -7239,39 +8175,45 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-2848619524</v>
+      </c>
+      <c r="C10">
+        <v>-2154381366</v>
+      </c>
+      <c r="D10">
         <v>-1524444388</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>-1138728580</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>-464800213</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-479944200</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>-374578926</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>-322919745</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-436940979</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-175178805</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>-132997035</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-53761414</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-35266611</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>-31808929</v>
       </c>
     </row>
@@ -7280,39 +8222,45 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-2492363864</v>
+      </c>
+      <c r="C11">
+        <v>-2471612750</v>
+      </c>
+      <c r="D11">
         <v>-2016131733</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>-2089637383</v>
       </c>
-      <c r="D11">
-        <v>-1728722046</v>
-      </c>
-      <c r="E11">
+      <c r="F11">
+        <v>-1728722045</v>
+      </c>
+      <c r="G11">
         <v>-1011758178</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>-433898719</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>5611457</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>100440513</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>108179568</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>-110349421</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>-107762811</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>-150851434</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>-127986888</v>
       </c>
     </row>
@@ -7321,39 +8269,45 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>3369015215</v>
+      </c>
+      <c r="C12">
+        <v>6777739265</v>
+      </c>
+      <c r="D12">
         <v>7851431487</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>7778072105</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>5283656200</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>5771253880</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>4939926815</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>257114178</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-586432642</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-166600639</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>-311209351</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>-262112439</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>103605764</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>72427581</v>
       </c>
     </row>
@@ -7377,39 +8331,45 @@
         <v xml:space="preserve">    Tasarruf Finansman Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B16">
+        <v>-21721778869</v>
+      </c>
+      <c r="C16">
+        <v>-13148977779</v>
+      </c>
+      <c r="D16">
         <v>-6764153198</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-4320352673</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>-2833238082</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-3548815066</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-2078919115</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-1355387575</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>-1018962735</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>-514836177</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>-375597490</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>-285351236</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>-538003373</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>-170517468</v>
       </c>
     </row>
@@ -7418,39 +8378,45 @@
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-968853908</v>
+      </c>
+      <c r="C17">
+        <v>278338656</v>
+      </c>
+      <c r="D17">
         <v>953410760</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>2686398396</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>2077220558</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>1379594171</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>697825759</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>-1288018307</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-1791910811</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-1120065360</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-669450855</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>-435508169</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>432785830</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>-57627119</v>
       </c>
     </row>
@@ -7464,33 +8430,39 @@
         <v xml:space="preserve">    Tasarruf Fon Havuzundaki Net Artış (Azalış)</v>
       </c>
       <c r="B19">
+        <v>23302186638</v>
+      </c>
+      <c r="C19">
+        <v>17783442281</v>
+      </c>
+      <c r="D19">
         <v>13960702100</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>9239964809</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>5888580331</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>6696424390</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>4835567592</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>2615260648</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>1648228552</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>1192283026</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>115581993</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>229098064</v>
       </c>
     </row>
@@ -7498,16 +8470,16 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>97632874</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>103003298</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>17405780</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>38825545</v>
       </c>
     </row>
@@ -7526,33 +8498,39 @@
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>2757461354</v>
+      </c>
+      <c r="C23">
+        <v>1864936107</v>
+      </c>
+      <c r="D23">
         <v>-298528175</v>
       </c>
-      <c r="C23">
+      <c r="E23">
         <v>155496785</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>136977150</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>1244050385</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1363605423</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>478579478</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>173014574</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>156653194</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>75835534</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>32648559</v>
       </c>
     </row>
@@ -7561,39 +8539,45 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>11817685104</v>
+      </c>
+      <c r="C24">
+        <v>14925940565</v>
+      </c>
+      <c r="D24">
         <v>13995462733</v>
       </c>
-      <c r="C24">
+      <c r="E24">
         <v>12071744085</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <v>8744992858</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>8192308241</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>6727896726</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>1873922071</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>497449207</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>758431563</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>191081789</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>29592468</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>286970450</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>240840154</v>
       </c>
     </row>
@@ -7601,7 +8585,7 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    İktisap Edilen İştirakler, Bağlı Ortaklıklar ve Birlikte Kontrol Edilen Ortaklıklar (İş Ortaklıkları)</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>-2802466048</v>
       </c>
     </row>
@@ -7615,39 +8599,45 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-8718343766</v>
+      </c>
+      <c r="C27">
+        <v>-8003699543</v>
+      </c>
+      <c r="D27">
         <v>-8987534381</v>
       </c>
-      <c r="C27">
+      <c r="E27">
         <v>-5358772594</v>
       </c>
-      <c r="D27">
+      <c r="F27">
         <v>-2298058024</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>-2292244165</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>-1032072229</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>-248295759</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>-252247201</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>-263814638</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>-188641170</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>-195766714</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>-161389319</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>-146540748</v>
       </c>
     </row>
@@ -7655,31 +8645,34 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Elden Çıkarılan Menkul ve Gayrimenkuller</v>
       </c>
-      <c r="B28">
+      <c r="C28">
+        <v>641774417</v>
+      </c>
+      <c r="D28">
         <v>641774418</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>930448868</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>288567054</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>288588435</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>16013963</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>24962904</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>30651846</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>19232823</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>10433488</v>
       </c>
     </row>
@@ -7713,39 +8706,45 @@
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>-8657798551</v>
+      </c>
+      <c r="C34">
+        <v>-7394903962</v>
+      </c>
+      <c r="D34">
         <v>-8723045692</v>
       </c>
-      <c r="C34">
+      <c r="E34">
         <v>-7114620789</v>
       </c>
-      <c r="D34">
+      <c r="F34">
         <v>-4777910502</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>-4806143159</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>-3229701592</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>-426821821</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>278078009</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>-238851734</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>-157989324</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>-176533891</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>-142114287</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>-136107260</v>
       </c>
     </row>
@@ -7758,10 +8757,13 @@
       <c r="A36" t="str">
         <v xml:space="preserve">    Krediler ve İhraç Edilen Menkul Değerlerden Kaynaklanan Nakit Çıkışı</v>
       </c>
-      <c r="B36">
+      <c r="C36">
+        <v>-925125572</v>
+      </c>
+      <c r="D36">
         <v>-1197239575</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>-1501732795</v>
       </c>
     </row>
@@ -7774,13 +8776,16 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Temettü Ödemeleri</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>-198000000</v>
       </c>
-      <c r="C38">
+      <c r="D38">
+        <v>-198000000</v>
+      </c>
+      <c r="E38">
         <v>-198000001</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>-284757731</v>
       </c>
     </row>
@@ -7789,39 +8794,45 @@
         <v xml:space="preserve">    Kiralamaya İlişkin Ödemeler</v>
       </c>
       <c r="B39">
-        <v>-94851523</v>
+        <v>-95129892</v>
       </c>
       <c r="C39">
-        <v>-101054479</v>
+        <v>-96874168</v>
       </c>
       <c r="D39">
-        <v>-97281318</v>
+        <v>-94851522</v>
       </c>
       <c r="E39">
-        <v>-79987201</v>
+        <v>-101054478</v>
       </c>
       <c r="F39">
+        <v>-97281317</v>
+      </c>
+      <c r="G39">
+        <v>-79987200</v>
+      </c>
+      <c r="H39">
         <v>-47669319</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>-33478614</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-29505881</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>-25490389</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>-13821533</v>
       </c>
-      <c r="K39">
+      <c r="M39">
         <v>-15829144</v>
       </c>
-      <c r="L39">
+      <c r="N39">
         <v>-14599024</v>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>-13523776</v>
       </c>
     </row>
@@ -7829,16 +8840,19 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="I40">
+      <c r="C40">
+        <v>-114500000</v>
+      </c>
+      <c r="K40">
         <v>30000000</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>-172623887</v>
       </c>
-      <c r="K40">
+      <c r="M40">
         <v>36650000</v>
       </c>
-      <c r="M40">
+      <c r="O40">
         <v>50000000</v>
       </c>
     </row>
@@ -7847,39 +8861,45 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
-        <v>-1604591098</v>
+        <v>-913826410</v>
       </c>
       <c r="C41">
-        <v>-2579138363</v>
+        <v>-1334499740</v>
       </c>
       <c r="D41">
-        <v>-2017943167</v>
+        <v>-1604591097</v>
       </c>
       <c r="E41">
-        <v>-1866477727</v>
+        <v>-2579138362</v>
       </c>
       <c r="F41">
+        <v>-2017943166</v>
+      </c>
+      <c r="G41">
+        <v>-1866477726</v>
+      </c>
+      <c r="H41">
         <v>-1622153005</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>-580967394</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>-187149031</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>101624192</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>173400211</v>
       </c>
-      <c r="K41">
+      <c r="M41">
         <v>380666487</v>
       </c>
-      <c r="L41">
+      <c r="N41">
         <v>35400976</v>
       </c>
-      <c r="M41">
+      <c r="O41">
         <v>36476224</v>
       </c>
     </row>
@@ -7887,7 +8907,7 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakde Eşdeğer Varlıklar Üzerindeki Etkisi</v>
       </c>
-      <c r="E42">
+      <c r="C42">
         <v>0</v>
       </c>
     </row>
@@ -7896,39 +8916,45 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
-        <v>3667825943</v>
+        <v>2246060143</v>
       </c>
       <c r="C43">
-        <v>2377984933</v>
+        <v>6196536863</v>
       </c>
       <c r="D43">
-        <v>1949139189</v>
+        <v>3667825944</v>
       </c>
       <c r="E43">
-        <v>1519687355</v>
+        <v>2377984934</v>
       </c>
       <c r="F43">
+        <v>1949139190</v>
+      </c>
+      <c r="G43">
+        <v>1519687356</v>
+      </c>
+      <c r="H43">
         <v>1876042129</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>866132856</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>588378185</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>621204021</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>206492676</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <v>233725064</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>180257139</v>
       </c>
-      <c r="M43">
+      <c r="O43">
         <v>141209118</v>
       </c>
     </row>
@@ -7944,7 +8970,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R45"/>
   </ignoredErrors>
 </worksheet>
 </file>